--- a/Test upload format/Mudra/IA/2026 - 2027- SHG/CP2 26-27  SHG.xlsx
+++ b/Test upload format/Mudra/IA/2026 - 2027- SHG/CP2 26-27  SHG.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>custid</t>
   </si>
@@ -89,7 +89,7 @@
     <t>HomeStay</t>
   </si>
   <si>
-    <t>SHG2627CR719</t>
+    <t>SHG2627CR711</t>
   </si>
   <si>
     <t>100000</t>
@@ -98,46 +98,37 @@
     <t>IA</t>
   </si>
   <si>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>01-04-2026</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>01-07-2027</t>
+  </si>
+  <si>
+    <t>SHG</t>
+  </si>
+  <si>
+    <t>SHG2627CR712</t>
+  </si>
+  <si>
+    <t>300000</t>
+  </si>
+  <si>
+    <t>SHG2627CR713</t>
+  </si>
+  <si>
     <t>400000</t>
   </si>
   <si>
-    <t>01-04-2026</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>SHG</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>SHG2627CR720</t>
-  </si>
-  <si>
-    <t>200000</t>
-  </si>
-  <si>
-    <t>SHG2627CR721</t>
-  </si>
-  <si>
-    <t>300000</t>
-  </si>
-  <si>
-    <t>SHG2627CR722</t>
-  </si>
-  <si>
-    <t>SHG2627CR723</t>
-  </si>
-  <si>
-    <t>SHG2627CR724</t>
-  </si>
-  <si>
-    <t>SHG2627CR711</t>
-  </si>
-  <si>
-    <t>SHG2627CR712</t>
+    <t>01-07-2028</t>
+  </si>
+  <si>
+    <t>SHG2627CR714</t>
   </si>
 </sst>
 </file>
@@ -311,7 +302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,109 +311,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,7 +662,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -701,16 +686,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -719,95 +704,95 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -822,13 +807,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1364,8 +1348,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T9"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <dimension ref="A1:T5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="27.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="26.8571428571429" customWidth="1"/>
@@ -1454,7 +1438,7 @@
       <c r="C2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F2" s="9" t="s">
@@ -1463,11 +1447,15 @@
       <c r="G2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="I2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
       <c r="K2" s="2">
         <v>1</v>
       </c>
@@ -1475,17 +1463,16 @@
         <v>1</v>
       </c>
       <c r="M2" s="11">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="2"/>
       <c r="S2" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:20">
@@ -1498,20 +1485,25 @@
       <c r="C3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="9" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="I3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
       <c r="K3" s="2">
         <v>1</v>
       </c>
@@ -1524,273 +1516,105 @@
       <c r="N3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="2"/>
       <c r="S3" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" spans="1:20">
+      <c r="A4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" s="13">
+        <v>1000000</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="12" t="s">
         <v>27</v>
       </c>
+      <c r="T4" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:20">
-      <c r="A4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="9" t="s">
+    <row r="5" s="3" customFormat="1" spans="1:20">
+      <c r="A5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="9" t="s">
+      <c r="F5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="2">
+      <c r="I5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="3">
         <v>1</v>
       </c>
-      <c r="L4" s="2">
+      <c r="K5" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="11">
-        <v>1000000</v>
-      </c>
-      <c r="N4" s="9" t="s">
+      <c r="L5" s="3">
+        <v>1</v>
+      </c>
+      <c r="M5" s="13">
+        <v>2000000</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="S4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="T4" s="2" t="s">
+      <c r="S5" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:20">
-      <c r="A5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="T5" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1</v>
-      </c>
-      <c r="M5" s="11">
-        <v>2000000</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="S5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:20">
-      <c r="A6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1</v>
-      </c>
-      <c r="M6" s="11">
-        <v>1000000</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="S6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:20">
-      <c r="A7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1</v>
-      </c>
-      <c r="M7" s="11">
-        <v>2000000</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" spans="1:20">
-      <c r="A8" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8" s="14">
-        <v>2000000</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:20">
-      <c r="A9" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="3">
-        <v>1</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1</v>
-      </c>
-      <c r="M9" s="14">
-        <v>2000000</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
